--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00727B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00727B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C94AE06-6741-4CBC-ABBA-95622685F65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C7AC86D-36BB-4468-8D33-6434E715A264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{261CEF39-109F-4309-9289-1B5433D11A4E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{058B0503-ECCA-4603-BE0C-5035D9AACD57}"/>
   </bookViews>
   <sheets>
     <sheet name="00727B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1621,25 +1621,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D26B8665-06C1-4202-B03B-C848252C76A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F2AFC16-D738-46C6-A75C-1C8EEADBCA9A}">
   <dimension ref="A1:R45"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1667,7 +1667,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1697,7 +1697,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1793,7 +1793,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1873,7 +1873,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>5.34</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>5.59</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>6.58</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2020</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>27</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>27</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>1.1399999999999999</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2019</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>27</v>
       </c>
@@ -3707,7 +3707,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>27</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>27</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="51">
         <v>2018</v>
       </c>
@@ -3873,7 +3873,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>27</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>27</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="49" t="s">
         <v>78</v>
       </c>
